--- a/行业涨跌停统计_每日追加.xlsx
+++ b/行业涨跌停统计_每日追加.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5607,6 +5607,3744 @@
       <c r="H123" t="inlineStr">
         <is>
           <t>9.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>688020</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>方邦股份</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>112.25</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>+18.71</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>11.48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>688661</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>和林微纳</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>103.44</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>+17.24</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>8.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>688268</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>华特气体</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>119.04</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>+19.84</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>12.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>301486</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>致尚科技</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>209.06</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>+34.84</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>29.32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>301511</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>德福科技</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>60.81</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>+7.95</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>+15.04%</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>14.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>317.51</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>+37.95</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>+13.57%</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>688548</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>广钢气体</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>29.50</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>+3.22</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>+12.25%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>7.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>301458</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>钧崴电子</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>+4.48</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>+11.97%</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>21.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>688707</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>振华新材</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>16.38</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>+1.74</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>+11.89%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>9.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>603115</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>海星股份</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>48.69</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>+4.43</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>+10.01%</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>002952</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>亚世光电</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>+2.48</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>8.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>603738</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>泰晶科技</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>34.67</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>+3.15</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>12.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>002993</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>奥海科技</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>49.20</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-5.47</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-10.01%</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>688270</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>臻镭科技</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>147.76</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-27.40</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-15.64%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>19.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>300533</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>冰川网络</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>30.58</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>+5.10</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>+20.02%</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>15.63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>688368</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>晶丰明源</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>156.36</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>+16.76</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>+12.01%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>7.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>600734</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>实达集团</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-10.10%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>8.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>000802</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>北京文化</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>+0.41</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>+10.12%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>4.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>600715</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>文投控股</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>+0.20</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>+9.90%</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>603272</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>联翔股份</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>24.79</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-9.99%</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>000056</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>皇庭国际</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>+0.19</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>+10.11%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>20.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>003027</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>同兴科技</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>+2.29</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>11.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>000715</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>中兴商业</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>6.27</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>+0.57</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>5.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>002081</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>金螳螂</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>+0.41</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>+10.05%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>4.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>600736</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>苏州高新</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>6.92</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>+0.63</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>603815</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>交建股份</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>+0.64</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>+9.95%</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>603030</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>全筑股份</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>+0.23</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>+9.83%</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>605178</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>时空科技</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>70.35</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-7.82</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-10.00%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>002670</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>国盛证券</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>13.21</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-10.01%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>301667</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>纳百川</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>115.90</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>+15.18</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>+15.07%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>54.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>000980</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>+0.22</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>+10.19%</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>603788</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>宁波高发</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>+1.59</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>+10.03%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>6.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>603178</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>圣龙股份</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>+1.92</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>11.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>603335</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>迪生力</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>7.37</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>+0.67</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>4.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>600699</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>均胜电子</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>28.71</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>+2.61</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>7.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>301022</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>海泰科</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>33.40</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>+5.57</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>+20.01%</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>300067</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>安诺其</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>+0.84</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>+19.95%</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>300801</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>泰和科技</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>30.88</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>+4.17</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>+15.61%</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>20.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>688106</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>金宏气体</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>+3.55</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>+12.20%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>14.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>301055</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>张小泉</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>+3.75</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>+12.00%</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>9.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>300081</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ST恒信</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>+0.36</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>+10.23%</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>600308</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>华泰股份</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>+0.38</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>+10.11%</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>002752</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>昇兴股份</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>+0.63</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>+10.05%</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>002950</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>奥美医疗</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>14.38</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>+1.31</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>8.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>002342</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>巨力索具</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>21.42</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>+1.95</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>30.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>603898</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>好莱客</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>14.50</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>+1.32</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>22.32</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>+2.03</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>12.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>002853</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>皮阿诺</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>29.03</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>+2.64</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>600261</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>阳光照明</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>+0.37</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>5.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>603016</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>新宏泰</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>55.23</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>+5.02</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>001268</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>联合精密</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>37.19</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>+3.38</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>15.28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>002846</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>英联股份</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>16.29</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>+1.48</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>7.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>002338</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>奥普光电</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>64.06</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>+5.82</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>603017</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>中衡设计</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>15.63</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>+1.42</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>5.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>003018</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>金富科技</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>47.45</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>+4.31</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>600520</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>三佳科技</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>30.50</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>+2.77</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>18.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>002361</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>22.69</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>+2.06</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>44.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>605365</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>立达信</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>27.65</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>+2.51</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>3.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>600103</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>青山纸业</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>+0.47</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>18.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>002418</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>康盛股份</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>6.13</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-9.99%</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>36.87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>002580</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>29.70</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-10.00%</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>108.97</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-12.11</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-10.00%</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>002825</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>纳尔股份</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-10.02%</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>6.32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>300834</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>星辉环材</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>38.40</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-6.29</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-14.07%</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>8.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>运输</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>运输</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>605298</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>必得科技</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>59.62</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>+5.42</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>运输</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>300123</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>亚光科技</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-19.94%</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>002201</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>九鼎新材</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>13.93</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>+1.27</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>+10.03%</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>15.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>600032</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>浙江新能</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>10.86</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>+0.99</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>+10.03%</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>000690</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>宝新能源</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>+0.48</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>11.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>600396</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>8.13</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>+0.74</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>+10.01%</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>20.61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>600678</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>四川金顶</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>11.87</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>+1.08</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>+10.01%</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>8.55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>600961</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>株冶集团</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>26.73</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>+2.43</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>000539</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>粤电力Ａ</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>+0.58</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>4.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>000819</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>岳阳兴长</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>17.08</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>+1.55</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>6.96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>600979</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>广安爱众</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>+0.48</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>+9.92%</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>15.37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>300435</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>中泰股份</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>24.42</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-11.90%</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>8.98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>002982</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>湘佳股份</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>15.54</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>+1.41</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>11.34%</t>
         </is>
       </c>
     </row>
@@ -5621,7 +9359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7847,6 +11585,1266 @@
       <c r="H53" t="inlineStr">
         <is>
           <t>18.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>301022</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>海泰科</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>33.40</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>+5.57</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>+20.01%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>300067</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>安诺其</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>+0.84</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>+19.95%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>300801</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>泰和科技</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>30.88</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>+4.17</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>+15.61%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>20.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>688106</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>金宏气体</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>+3.55</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>+12.20%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>14.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>301055</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>张小泉</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>+3.75</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>+12.00%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>9.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>300081</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ST恒信</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>+0.36</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>+10.23%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>600308</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>华泰股份</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>+0.38</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>+10.11%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>002752</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>昇兴股份</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>+0.63</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>+10.05%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>002950</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>奥美医疗</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>14.38</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>+1.31</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>8.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>002342</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>巨力索具</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>21.42</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>+1.95</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>30.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>603898</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>好莱客</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>14.50</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>+1.32</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>22.32</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>+2.03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>12.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>002853</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>皮阿诺</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>29.03</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>+2.64</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>600261</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>阳光照明</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>+0.37</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>5.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>603016</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>新宏泰</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>55.23</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>+5.02</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>001268</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>联合精密</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>37.19</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>+3.38</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>15.28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>002846</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>英联股份</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>16.29</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>+1.48</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>7.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>002338</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>奥普光电</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>64.06</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>+5.82</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>603017</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>中衡设计</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>15.63</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>+1.42</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>5.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>003018</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>金富科技</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>47.45</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>+4.31</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>600520</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>三佳科技</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>30.50</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>+2.77</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>002361</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>22.69</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>+2.06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>44.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>605365</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>立达信</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>27.65</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>+2.51</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>600103</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>青山纸业</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>+0.47</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>18.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>002418</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>康盛股份</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>6.13</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-9.99%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>36.87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>002580</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>29.70</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-10.00%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>108.97</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-12.11</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-10.00%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>002825</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>纳尔股份</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-10.02%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>6.32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>制造</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>300834</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>星辉环材</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>38.40</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-6.29</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-14.07%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>8.62%</t>
         </is>
       </c>
     </row>
@@ -7861,7 +12859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8029,6 +13027,132 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>4.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>运输</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>运输</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>605298</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>必得科技</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>59.62</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+5.42</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>运输</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>300123</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>亚光科技</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-19.94%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -8043,7 +13167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8589,6 +13713,468 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>5.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>002201</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>九鼎新材</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>13.93</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>+1.27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>+10.03%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>15.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>600032</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>浙江新能</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10.86</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>+0.99</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>+10.03%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>000690</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>宝新能源</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>+0.48</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>11.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>600396</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8.13</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>+0.74</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>+10.01%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>20.61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>600678</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>四川金顶</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>11.87</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>+1.08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>+10.01%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8.55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>600961</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>株冶集团</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>26.73</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+2.43</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>000539</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>粤电力Ａ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>+0.58</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>000819</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>岳阳兴长</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>17.08</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+1.55</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6.96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>600979</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>广安爱众</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+0.48</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+9.92%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>15.37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>300435</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>中泰股份</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>24.42</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.90%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>8.98%</t>
         </is>
       </c>
     </row>
@@ -8603,7 +14189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8813,6 +14399,90 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>9.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>002982</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>湘佳股份</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15.54</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>+1.41</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>11.34%</t>
         </is>
       </c>
     </row>
@@ -8860,7 +14530,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8869,19 +14539,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8890,19 +14560,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8923,7 +14593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8944,7 +14614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8953,19 +14623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8986,7 +14656,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8995,10 +14665,10 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -9007,7 +14677,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9016,19 +14686,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9037,19 +14707,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9058,10 +14728,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -9070,7 +14740,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9079,19 +14749,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9100,13 +14770,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9194,12 +14864,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>日期类型股东数占比2026-04-20赚钱股东数18300.4万人64%2026-04-20亏钱股东数9075.8万人32%2026-04-20不亏不赚股东数1196.1万人4%</t>
+          <t>日期类型股东数占比2026-04-21赚钱股东数9628.1万人34%2026-04-21亏钱股东数18139.8万人63%2026-04-21不亏不赚股东数845.0万人3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9221,7 +14891,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9248,12 +14918,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9263,24 +14933,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18300.4万人</t>
+          <t>9628.1万人</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9290,24 +14960,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9075.8万人</t>
+          <t>18139.8万人</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>63%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9317,12 +14987,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1196.1万人</t>
+          <t>845.0万人</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
@@ -9365,29 +15035,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>化学纤维制造业</t>
+          <t>煤炭开采和洗选业</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+2.63%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9397,7 +15067,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9409,51 +15079,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>林业</t>
+          <t>广播、电视、电影和影视录音制作业</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>农业</t>
+          <t>教育</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9463,7 +15133,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9475,990 +15145,990 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>仓储业</t>
+          <t>皮革、毛皮、羽毛及其制品和制鞋业</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>铁路、船舶、航空航天和其他运输设备制造业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+1.37%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>废弃资源综合利用业</t>
+          <t>石油加工、炼焦和核燃料加工业</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建筑装饰和其他建筑业</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>道路运输业</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>有色金属矿采选业</t>
+          <t>水的生产和供应业</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>新闻和出版业</t>
+          <t>货币金融服务</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>有色金属冶炼和压延加工业</t>
+          <t>邮政业</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>航空运输业</t>
+          <t>铁路运输业</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>电气机械和器材制造业</t>
+          <t>水上运输业</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>互联网和相关服务</t>
+          <t>有色金属矿采选业</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>燃气生产和供应业</t>
+          <t>家具制造业</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>卫生</t>
+          <t>纺织服装、服饰业</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>专业技术服务业</t>
+          <t>畜牧业</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>邮政业</t>
+          <t>化学原料和化学制品制造业</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>377</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>渔业</t>
+          <t>纺织业</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+1.10%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>农副食品加工业</t>
+          <t>燃气生产和供应业</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>+1.10%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>非金属矿物制品业</t>
+          <t>土木工程建筑业</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>+1.10%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>建筑装饰和其他建筑业</t>
+          <t>农副食品加工业</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>仪器仪表制造业</t>
+          <t>装卸搬运和运输代理业</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>计算机、通信和其他电子设备制造业</t>
+          <t>航空运输业</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>生态保护和环境治理业</t>
+          <t>化学纤维制造业</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>家具制造业</t>
+          <t>金属制品业</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>纺织业</t>
+          <t>新闻和出版业</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>商务服务业</t>
+          <t>非金属矿物制品业</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>橡胶和塑料制品业</t>
+          <t>文化艺术业</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>印刷和记录媒介复制业</t>
+          <t>生态保护和环境治理业</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>纺织服装、服饰业</t>
+          <t>石油和天然气开采业</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他金融业</t>
+          <t>计算机、通信和其他电子设备制造业</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>666</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>货币金融服务</t>
+          <t>食品制造业</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>文化艺术业</t>
+          <t>有色金属冶炼和压延加工业</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>土木工程建筑业</t>
+          <t>房地产业</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>软件和信息技术服务业</t>
+          <t>批发业</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>水的生产和供应业</t>
+          <t>专业技术服务业</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>石油加工、炼焦和核燃料加工业</t>
+          <t>黑色金属冶炼和压延加工业</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>专用设备制造业</t>
+          <t>仓储业</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>装卸搬运和运输代理业</t>
+          <t>专用设备制造业</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>409</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>酒、饮料和精制茶制造业</t>
+          <t>住宿业</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>其他制造业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>批发业</t>
+          <t>汽车制造业</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>207</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>金属制品业</t>
+          <t>仪器仪表制造业</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>化学原料和化学制品制造业</t>
+          <t>木材加工和木、竹、藤、棕、草制品业</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>汽车制造业</t>
+          <t>其他制造业</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>研究和试验发展</t>
+          <t>酒、饮料和精制茶制造业</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>道路运输业</t>
+          <t>零售业</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -10473,7 +16143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11313,6 +16983,636 @@
       <c r="H20" t="inlineStr">
         <is>
           <t>25.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>688020</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>方邦股份</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>112.25</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+18.71</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>11.48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>688661</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>和林微纳</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>103.44</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+17.24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>8.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>688268</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>华特气体</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>119.04</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>+19.84</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>12.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>301486</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>致尚科技</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>209.06</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>+34.84</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>+20.00%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>29.32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>301511</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>德福科技</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>60.81</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+7.95</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>+15.04%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>14.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>317.51</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>+37.95</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>+13.57%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>688548</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>广钢气体</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>29.50</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>+3.22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>+12.25%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>7.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>301458</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>钧崴电子</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+4.48</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>+11.97%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>21.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>688707</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>振华新材</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16.38</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>+1.74</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>+11.89%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>9.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>603115</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>海星股份</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>48.69</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>+4.43</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>+10.01%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>002952</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>亚世光电</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>+2.48</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>603738</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>泰晶科技</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>34.67</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>+3.15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>12.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>002993</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>奥海科技</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>49.20</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-5.47</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-10.01%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>硬科</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>688270</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>臻镭科技</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>147.76</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-27.40</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-15.64%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>19.04%</t>
         </is>
       </c>
     </row>
@@ -11327,7 +17627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11705,6 +18005,174 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>0.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>300533</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>冰川网络</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>30.58</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>+5.10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>+20.02%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>15.63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>688368</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>晶丰明源</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>156.36</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+16.76</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>+12.01%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>软科</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>600734</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>实达集团</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-10.10%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>8.24%</t>
         </is>
       </c>
     </row>
@@ -11719,7 +18187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11801,6 +18269,48 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>换手率</t>
         </is>
@@ -11817,7 +18327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12027,6 +18537,174 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>0.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>000802</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>北京文化</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>+0.41</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+10.12%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>600715</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>文投控股</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+0.20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+9.90%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>文教</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>603272</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>联翔股份</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24.79</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.99%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -12041,7 +18719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12419,6 +19097,174 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>7.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>000056</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>皇庭国际</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>+0.19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>+10.11%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>20.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>003027</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>同兴科技</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+2.29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>11.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>其他（共413家）</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>000715</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>中兴商业</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6.27</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>+0.57</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5.54%</t>
         </is>
       </c>
     </row>
@@ -12433,7 +19279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12727,6 +19573,258 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>2.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>002081</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>金螳螂</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>+0.41</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>+10.05%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>600736</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>苏州高新</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6.92</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>+0.63</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>603815</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>交建股份</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>+0.64</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>+9.95%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>603030</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>全筑股份</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+0.23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>+9.83%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>地产</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>605178</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>时空科技</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>70.35</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-7.82</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-10.00%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -12741,7 +19839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12867,6 +19965,90 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>2.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>002670</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>国盛证券</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13.21</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-10.01%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -12881,7 +20063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13052,6 +20234,300 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>涨跌</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>涨跌幅</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>换手率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>301667</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>纳百川</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>115.90</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+15.18</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+15.07%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>54.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>000980</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>+0.22</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+10.19%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>603788</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>宁波高发</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+1.59</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+10.03%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>603178</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>圣龙股份</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>+1.92</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>11.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>603335</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>迪生力</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.37</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>+0.67</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>600699</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>均胜电子</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>28.71</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>+2.61</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7.67%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
